--- a/models/holdings/LNG_Valuation.xlsx
+++ b/models/holdings/LNG_Valuation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t xml:space="preserve">Cheniere Energy (LNG): valuation summary</t>
   </si>
@@ -79,30 +79,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sell on a cut to cash flow guidance, or if new long-term contracting stalls as the 2027 to 2028 LNG supply wave arrives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levels follow the rules on the positions page and are reset when the model changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base value is what the business is worth if the base case plays out and you want to earn the discount rate. Implied return is what the base case earns at today's price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF: five explicit years, then five years fading growth, margin and reinvestment to terminal levels. FCF = operating income x (1 - tax) - net reinvestment - working capital x revenue change. Mid-year discounting from October 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margins are after stock-based pay. For ServiceNow that is about 19% today, not the 31.5% non-GAAP figure, which is the main reason its value is lower than a multiple of adjusted earnings suggests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks: tangible book plus the present value of returns above the cost of equity (residual income). TMC: probability-weighted, from the company's 2025 study with analyst haircuts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount rates use a 5.31% risk-free rate and a 5% equity risk premium, the same as the earlier journal models. At these rates most quality stocks look fully priced; the implied return column shows by how much.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price and data dates are on the model sheet. Company data: Stock Analysis, company filings and releases. Research for my own records, not investment advice.</t>
   </si>
   <si>
     <t xml:space="preserve">Cheniere Energy (LNG): 10-year scenario DCF</t>
@@ -436,7 +412,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -444,9 +420,8 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="General"/>
-    <numFmt numFmtId="172" formatCode="0.00"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -575,11 +550,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,51 +566,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -639,63 +618,59 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -954,170 +929,142 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <f aca="false">LNG!B4</f>
         <v>297.605</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">LNG!B10</f>
         <v>0.075</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <f aca="false">LNG!B75</f>
         <v>135.17044339531</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">LNG!B76</f>
         <v>305.060649546943</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">LNG!B77</f>
         <v>441.024677778915</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
         <v>0.0250521649399122</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <f aca="false">LNG!B86</f>
         <v>0.0762688670296594</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
         <v>305</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>305</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>440</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1137,253 +1084,253 @@
   <dimension ref="A1:L86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>297.605</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.20653</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B7" s="13" t="n">
+        <v>-26.85</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>297.605</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B8" s="13" t="n">
+        <v>-15.82</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="10" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B9" s="14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>0.20653</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>-26.85</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>-15.82</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
         <v>0.075</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="C15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D15" s="17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="E15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="F15" s="17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="G15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="H15" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="I15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="J15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="K15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="L15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="16" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="1" t="n">
         <f aca="false">B16+1</f>
         <v>1.5</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">C16+1</f>
         <v>2.5</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">D16+1</f>
         <v>3.5</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="1" t="n">
         <f aca="false">E16+1</f>
         <v>4.5</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="1" t="n">
         <f aca="false">F16+1</f>
         <v>5.5</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">G16+1</f>
         <v>6.5</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I16" s="1" t="n">
         <f aca="false">H16+1</f>
         <v>7.5</v>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="1" t="n">
         <f aca="false">I16+1</f>
         <v>8.5</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="K16" s="1" t="n">
         <f aca="false">J16+1</f>
         <v>9.5</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="0" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -1397,23 +1344,23 @@
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="12" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <v>20.5</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>21.5</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>22.5</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <v>23.5</v>
       </c>
       <c r="G20" s="20" t="n">
@@ -1441,47 +1388,47 @@
         <v>26.1673805545604</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="6" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="n">
         <f aca="false">B20/$B$12-1</f>
         <v>-0.0707964601769913</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <f aca="false">C20/B20-1</f>
         <v>-0.0238095238095238</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <f aca="false">D20/C20-1</f>
         <v>0.0487804878048781</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <f aca="false">E20/D20-1</f>
         <v>0.0465116279069768</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <f aca="false">F20/E20-1</f>
         <v>0.0444444444444445</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <f aca="false">G20/F20-1</f>
         <v>0.0365555555555557</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <f aca="false">H20/G20-1</f>
         <v>0.0286666666666666</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <f aca="false">I20/H20-1</f>
         <v>0.0207777777777778</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <f aca="false">J20/I20-1</f>
         <v>0.012888888888889</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <f aca="false">K20/J20-1</f>
         <v>0.00499999999999989</v>
       </c>
@@ -1489,9 +1436,9 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>67</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>0.29</v>
@@ -1508,23 +1455,23 @@
       <c r="F22" s="22" t="n">
         <v>0.28</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*G$17/5</f>
         <v>0.278</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*H$17/5</f>
         <v>0.276</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*I$17/5</f>
         <v>0.274</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*J$17/5</f>
         <v>0.272</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*K$17/5</f>
         <v>0.27</v>
       </c>
@@ -1532,9 +1479,9 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>68</v>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">B20*B22</f>
@@ -1581,9 +1528,9 @@
         <v>7.0651927497313</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>69</v>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">B23*(1-$B$9)</f>
@@ -1630,9 +1577,9 @@
         <v>5.79345805477967</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>70</v>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B25" s="22" t="n">
         <v>0.08</v>
@@ -1649,23 +1596,23 @@
       <c r="F25" s="22" t="n">
         <v>0.02</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*G$17/5</f>
         <v>0.019</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*H$17/5</f>
         <v>0.018</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*I$17/5</f>
         <v>0.017</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*J$17/5</f>
         <v>0.016</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*K$17/5</f>
         <v>0.015</v>
       </c>
@@ -1673,9 +1620,9 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>71</v>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B26" s="20" t="n">
         <f aca="false">B20*B25</f>
@@ -1722,9 +1669,9 @@
         <v>0.392510708318406</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>72</v>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B27" s="20" t="n">
         <f aca="false">$B$11*(B20-$B$12)</f>
@@ -1771,9 +1718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>73</v>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B28" s="20" t="n">
         <f aca="false">B24-B26-B27</f>
@@ -1820,9 +1767,9 @@
         <v>5.40094734646126</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>74</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -1865,9 +1812,9 @@
         <v>0.503059771960701</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>75</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
@@ -1911,58 +1858,58 @@
       </c>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>76</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
         <v>77.1563906637323</v>
       </c>
-      <c r="C31" s="0" t="str">
+      <c r="C31" s="1" t="str">
         <f aca="false">IF($B$10&gt;L21,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>77</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
         <v>38.8142762926079</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>78</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
         <v>27.9167516744334</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>79</v>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
         <v>135.17044339531</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="6" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
         <v>-0.545805872228927</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -1976,23 +1923,23 @@
       <c r="K37" s="19"/>
       <c r="L37" s="19"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="12" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="13" t="n">
         <v>23.4</v>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="13" t="n">
         <v>24.6</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="13" t="n">
         <v>25.8</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>27.2</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>28.6</v>
       </c>
       <c r="G38" s="20" t="n">
@@ -2020,47 +1967,47 @@
         <v>33.5769262385969</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="6" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="7" t="n">
         <f aca="false">B38/$B$12-1</f>
         <v>0.0353982300884954</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="7" t="n">
         <f aca="false">C38/B38-1</f>
         <v>0.0512820512820513</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <f aca="false">D38/C38-1</f>
         <v>0.0487804878048781</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <f aca="false">E38/D38-1</f>
         <v>0.0542635658914727</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <f aca="false">F38/E38-1</f>
         <v>0.0514705882352942</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <f aca="false">G38/F38-1</f>
         <v>0.0441764705882353</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <f aca="false">H38/G38-1</f>
         <v>0.0368823529411766</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <f aca="false">I38/H38-1</f>
         <v>0.0295882352941177</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="7" t="n">
         <f aca="false">J38/I38-1</f>
         <v>0.0222941176470588</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="7" t="n">
         <f aca="false">K38/J38-1</f>
         <v>0.0149999999999999</v>
       </c>
@@ -2068,9 +2015,9 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>67</v>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.31</v>
@@ -2087,23 +2034,23 @@
       <c r="F40" s="22" t="n">
         <v>0.31</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*G$17/5</f>
         <v>0.306</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*H$17/5</f>
         <v>0.302</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*I$17/5</f>
         <v>0.298</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*J$17/5</f>
         <v>0.294</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*K$17/5</f>
         <v>0.29</v>
       </c>
@@ -2111,9 +2058,9 @@
         <v>0.29</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>68</v>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">B38*B40</f>
@@ -2160,9 +2107,9 @@
         <v>9.7373086091931</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>69</v>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B42" s="20" t="n">
         <f aca="false">B41*(1-$B$9)</f>
@@ -2209,9 +2156,9 @@
         <v>7.98459305953834</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>70</v>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.08</v>
@@ -2228,23 +2175,23 @@
       <c r="F43" s="22" t="n">
         <v>0.02</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*G$17/5</f>
         <v>0.019</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*H$17/5</f>
         <v>0.018</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*I$17/5</f>
         <v>0.017</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*J$17/5</f>
         <v>0.016</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*K$17/5</f>
         <v>0.015</v>
       </c>
@@ -2252,9 +2199,9 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>71</v>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">B38*B43</f>
@@ -2301,9 +2248,9 @@
         <v>0.503653893578953</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>72</v>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B45" s="20" t="n">
         <f aca="false">$B$11*(B38-$B$12)</f>
@@ -2350,9 +2297,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>73</v>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B46" s="20" t="n">
         <f aca="false">B42-B44-B45</f>
@@ -2399,9 +2346,9 @@
         <v>7.48093916595939</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>74</v>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2444,9 +2391,9 @@
         <v>0.503059771960701</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>75</v>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
@@ -2490,58 +2437,58 @@
       </c>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>76</v>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
         <v>124.682319432656</v>
       </c>
-      <c r="C49" s="0" t="str">
+      <c r="C49" s="1" t="str">
         <f aca="false">IF($B$10&gt;L39,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>77</v>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
         <v>62.7226591813234</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>78</v>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
         <v>63.0041759509301</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>79</v>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
         <v>305.060649546943</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="6" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
         <v>0.0250521649399122</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -2555,23 +2502,23 @@
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="12" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="C56" s="12" t="n">
+      <c r="C56" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="D56" s="12" t="n">
+      <c r="D56" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="E56" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="F56" s="13" t="n">
         <v>32</v>
       </c>
       <c r="G56" s="20" t="n">
@@ -2599,47 +2546,47 @@
         <v>39.4417121865586</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="6" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="7" t="n">
         <f aca="false">B56/$B$12-1</f>
         <v>0.0619469026548671</v>
       </c>
-      <c r="C57" s="6" t="n">
+      <c r="C57" s="7" t="n">
         <f aca="false">C56/B56-1</f>
         <v>0.0833333333333333</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="7" t="n">
         <f aca="false">D56/C56-1</f>
         <v>0.0769230769230769</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="7" t="n">
         <f aca="false">E56/D56-1</f>
         <v>0.0714285714285714</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="7" t="n">
         <f aca="false">F56/E56-1</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G57" s="7" t="n">
         <f aca="false">G56/F56-1</f>
         <v>0.0573333333333332</v>
       </c>
-      <c r="H57" s="6" t="n">
+      <c r="H57" s="7" t="n">
         <f aca="false">H56/G56-1</f>
         <v>0.048</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" s="7" t="n">
         <f aca="false">I56/H56-1</f>
         <v>0.0386666666666666</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="7" t="n">
         <f aca="false">J56/I56-1</f>
         <v>0.0293333333333334</v>
       </c>
-      <c r="K57" s="6" t="n">
+      <c r="K57" s="7" t="n">
         <f aca="false">K56/J56-1</f>
         <v>0.02</v>
       </c>
@@ -2647,9 +2594,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>67</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B58" s="22" t="n">
         <v>0.32</v>
@@ -2666,23 +2613,23 @@
       <c r="F58" s="22" t="n">
         <v>0.33</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*G$17/5</f>
         <v>0.326</v>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="H58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*H$17/5</f>
         <v>0.322</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*I$17/5</f>
         <v>0.318</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*J$17/5</f>
         <v>0.314</v>
       </c>
-      <c r="K58" s="6" t="n">
+      <c r="K58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*K$17/5</f>
         <v>0.31</v>
       </c>
@@ -2690,9 +2637,9 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>68</v>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B59" s="20" t="n">
         <f aca="false">B56*B58</f>
@@ -2739,9 +2686,9 @@
         <v>12.2269307778332</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>69</v>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B60" s="20" t="n">
         <f aca="false">B59*(1-$B$9)</f>
@@ -2788,9 +2735,9 @@
         <v>10.0260832378232</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>70</v>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B61" s="22" t="n">
         <v>0.09</v>
@@ -2807,23 +2754,23 @@
       <c r="F61" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*G$17/5</f>
         <v>0.028</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*H$17/5</f>
         <v>0.026</v>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*I$17/5</f>
         <v>0.024</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*J$17/5</f>
         <v>0.022</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="K61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*K$17/5</f>
         <v>0.02</v>
       </c>
@@ -2831,9 +2778,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>71</v>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B62" s="20" t="n">
         <f aca="false">B56*B61</f>
@@ -2880,9 +2827,9 @@
         <v>0.788834243731172</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>72</v>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B63" s="20" t="n">
         <f aca="false">$B$11*(B56-$B$12)</f>
@@ -2929,9 +2876,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>73</v>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B64" s="20" t="n">
         <f aca="false">B60-B62-B63</f>
@@ -2978,9 +2925,9 @@
         <v>9.23724899409203</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>74</v>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -3023,9 +2970,9 @@
         <v>0.503059771960701</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>75</v>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
@@ -3069,62 +3016,62 @@
       </c>
       <c r="L66" s="20"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>76</v>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
         <v>167.949981710764</v>
       </c>
-      <c r="C67" s="0" t="str">
+      <c r="C67" s="1" t="str">
         <f aca="false">IF($B$10&gt;L57,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>77</v>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
         <v>84.4888795002209</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>78</v>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
         <v>91.0848267016793</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>79</v>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
         <v>441.024677778915</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="6" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
         <v>0.481912863624317</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
@@ -3136,207 +3083,207 @@
       <c r="K74" s="19"/>
       <c r="L74" s="19"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B75" s="7" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
         <v>135.17044339531</v>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
         <v>-0.545805872228927</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="7" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
         <v>305.060649546943</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
         <v>0.0250521649399122</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B77" s="7" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
         <v>441.024677778915</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
         <v>0.481912863624317</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B78" s="7" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
         <v>305.060649546943</v>
       </c>
-      <c r="C78" s="6" t="n">
+      <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
         <v>0.0250521649399122</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>89</v>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
         <v>0.593547653595603</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B82" s="13" t="n">
+      <c r="B82" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="C82" s="13" t="n">
+      <c r="C82" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="14" t="n">
         <v>0.07</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="14" t="n">
         <v>0.08</v>
       </c>
-      <c r="F82" s="13" t="n">
+      <c r="F82" s="14" t="n">
         <v>0.09</v>
       </c>
-      <c r="G82" s="13" t="n">
+      <c r="G82" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="H82" s="13" t="n">
+      <c r="H82" s="14" t="n">
         <v>0.11</v>
       </c>
-      <c r="I82" s="13" t="n">
+      <c r="I82" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="J82" s="13" t="n">
+      <c r="J82" s="14" t="n">
         <v>0.13</v>
       </c>
-      <c r="K82" s="13" t="n">
+      <c r="K82" s="14" t="n">
         <v>0.14</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="7" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B83" s="8" t="n">
         <f aca="false">IF(B82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+B82)^$B$16:$K$16)+$L46/(B82-$L39)/(1+B82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>678.564795340189</v>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="8" t="n">
         <f aca="false">IF(C82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+C82)^$B$16:$K$16)+$L46/(C82-$L39)/(1+C82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>479.257586455029</v>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D83" s="8" t="n">
         <f aca="false">IF(D82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+D82)^$B$16:$K$16)+$L46/(D82-$L39)/(1+D82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>352.541019348523</v>
       </c>
-      <c r="E83" s="7" t="n">
+      <c r="E83" s="8" t="n">
         <f aca="false">IF(E82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+E82)^$B$16:$K$16)+$L46/(E82-$L39)/(1+E82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>264.907928570543</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <f aca="false">IF(F82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+F82)^$B$16:$K$16)+$L46/(F82-$L39)/(1+F82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>200.721745461392</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <f aca="false">IF(G82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+G82)^$B$16:$K$16)+$L46/(G82-$L39)/(1+G82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>151.70438330211</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <f aca="false">IF(H82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+H82)^$B$16:$K$16)+$L46/(H82-$L39)/(1+H82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>113.063352117941</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <f aca="false">IF(I82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+I82)^$B$16:$K$16)+$L46/(I82-$L39)/(1+I82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>81.8319501680315</v>
       </c>
-      <c r="J83" s="7" t="n">
+      <c r="J83" s="8" t="n">
         <f aca="false">IF(J82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+J82)^$B$16:$K$16)+$L46/(J82-$L39)/(1+J82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>56.0754420679196</v>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="K83" s="8" t="n">
         <f aca="false">IF(K82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+K82)^$B$16:$K$16)+$L46/(K82-$L39)/(1+K82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>34.4782711100344</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" s="6" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="n">
         <f aca="false">IFERROR(B83/$B$4-1,"n/a")</f>
         <v>1.28008533237072</v>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C84" s="7" t="n">
         <f aca="false">IFERROR(C83/$B$4-1,"n/a")</f>
         <v>0.610381500495722</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="7" t="n">
         <f aca="false">IFERROR(D83/$B$4-1,"n/a")</f>
         <v>0.184593737835461</v>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <f aca="false">IFERROR(E83/$B$4-1,"n/a")</f>
         <v>-0.109867345741694</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="7" t="n">
         <f aca="false">IFERROR(F83/$B$4-1,"n/a")</f>
         <v>-0.325543100884084</v>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="G84" s="7" t="n">
         <f aca="false">IFERROR(G83/$B$4-1,"n/a")</f>
         <v>-0.490249211867711</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" s="7" t="n">
         <f aca="false">IFERROR(H83/$B$4-1,"n/a")</f>
         <v>-0.620089205094199</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="7" t="n">
         <f aca="false">IFERROR(I83/$B$4-1,"n/a")</f>
         <v>-0.725031668930188</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="7" t="n">
         <f aca="false">IFERROR(J83/$B$4-1,"n/a")</f>
         <v>-0.811577621115507</v>
       </c>
-      <c r="K84" s="6" t="n">
+      <c r="K84" s="7" t="n">
         <f aca="false">IFERROR(K83/$B$4-1,"n/a")</f>
         <v>-0.884147540834212</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8" t="s">
-        <v>92</v>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="B86" s="26" t="n">
         <f aca="false">IFERROR(IF(MATCH($B$4,$B$83:$K$83,-1)=10,"above 14%",INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1))+(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-$B$4)/(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1)+1))*(INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)+1)-INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)))),"below 5%")</f>
         <v>0.0762688670296594</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>93</v>
+      <c r="C86" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3358,277 +3305,277 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B8" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B9" s="14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B12" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C12" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.0531</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>0.06</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>109</v>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B14" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>111</v>
+      <c r="C14" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">0.67*IF(ISNUMBER(B14),B14,B13)+0.33</f>
         <v>0.866</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>113</v>
+      <c r="C15" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">IF($B$6=1,IF(ISNUMBER(B14),B14,B13),B15)</f>
         <v>0.866</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>115</v>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
         <v>0.0964</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>117</v>
+      <c r="C17" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
         <v>0.0651</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="n">
+      <c r="C18" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6" t="n">
         <f aca="false">LNG!B9</f>
         <v>0.18</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>120</v>
+      <c r="C19" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
         <v>0.053382</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>121</v>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">LNG!B4*LNG!B6</f>
         <v>61.46436065</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>123</v>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>27.97</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>125</v>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">B21/(B21+B22)</f>
         <v>0.687256667384696</v>
       </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>126</v>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22/(B21+B22)</f>
         <v>0.312743332615304</v>
       </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>127</v>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
         <v>0.0829464073175549</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>129</v>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="B26" s="31" t="n">
         <v>0.075</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>131</v>
+      <c r="C26" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
         <v>0.075</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="0" t="str">
+      <c r="C27" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="1" t="str">
         <f aca="false">IF(B27&gt;MAX(LNG!L21,LNG!L39,LNG!L57),"OK","WACC must exceed growth")</f>
         <v>OK</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>134</v>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
         <v>0.075</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>135</v>
+      <c r="C29" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/models/holdings/LNG_Valuation.xlsx
+++ b/models/holdings/LNG_Valuation.xlsx
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Risk-free rate (10-year Treasury)</t>
   </si>
   <si>
-    <t xml:space="preserve">FRED via MacroRadar, Oct 6, 2026 (same as earlier journal models)</t>
+    <t xml:space="preserve">10-year Treasury yield at the close on 2026-10-28; assumed rates below move with it</t>
   </si>
   <si>
     <t xml:space="preserve">Equity risk premium</t>
@@ -989,23 +989,23 @@
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">LNG!B10</f>
-        <v>0.075</v>
+        <v>0.0722</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">LNG!B75</f>
-        <v>135.17044339531</v>
+        <v>149.896015253973</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">LNG!B76</f>
-        <v>305.060649546943</v>
+        <v>330.62375234843</v>
       </c>
       <c r="G5" s="5" t="n">
         <f aca="false">LNG!B77</f>
-        <v>441.024677778915</v>
+        <v>476.978442289789</v>
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
-        <v>0.0250521649399122</v>
+        <v>0.110948244647871</v>
       </c>
       <c r="I5" s="6" t="n">
         <f aca="false">LNG!B86</f>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
-        <v>305</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
-        <v>0.075</v>
+        <v>0.0722</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
@@ -1773,43 +1773,43 @@
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.964485644340824</v>
+        <v>0.965744177733016</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.897195948224023</v>
+        <v>0.900712719392852</v>
       </c>
       <c r="D29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.834600882068858</v>
+        <v>0.840060361306521</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.776372913552426</v>
+        <v>0.78349222281899</v>
       </c>
       <c r="F29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.722207361444118</v>
+        <v>0.730733280002789</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.671820801343365</v>
+        <v>0.681527028542053</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.624949582644991</v>
+        <v>0.635634236655524</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.581348448972085</v>
+        <v>0.592831781995452</v>
       </c>
       <c r="J29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.540789254857753</v>
+        <v>0.55291156686761</v>
       </c>
       <c r="K29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.503059771960701</v>
+        <v>0.515679506498424</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1818,43 +1818,43 @@
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
-        <v>3.19611252821662</v>
+        <v>3.20028305617167</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">C28*C29</f>
-        <v>2.93544570339936</v>
+        <v>2.94695187530953</v>
       </c>
       <c r="D30" s="20" t="n">
         <f aca="false">D28*D29</f>
-        <v>3.22272784602069</v>
+        <v>3.243809079149</v>
       </c>
       <c r="E30" s="20" t="n">
         <f aca="false">E28*E29</f>
-        <v>3.48669075476395</v>
+        <v>3.51866357268009</v>
       </c>
       <c r="F30" s="20" t="n">
         <f aca="false">F28*F29</f>
-        <v>3.55730457952915</v>
+        <v>3.59929984398174</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">G28*G29</f>
-        <v>3.41961372986095</v>
+        <v>3.46901908874149</v>
       </c>
       <c r="H30" s="20" t="n">
         <f aca="false">H28*H29</f>
-        <v>3.26220359637615</v>
+        <v>3.31797692226857</v>
       </c>
       <c r="I30" s="20" t="n">
         <f aca="false">I28*I29</f>
-        <v>3.0881437853908</v>
+        <v>3.14914366175478</v>
       </c>
       <c r="J30" s="20" t="n">
         <f aca="false">J28*J29</f>
-        <v>2.90075092743944</v>
+        <v>2.96577405334188</v>
       </c>
       <c r="K30" s="20" t="n">
         <f aca="false">K28*K29</f>
-        <v>2.70348193082841</v>
+        <v>2.77130135546977</v>
       </c>
       <c r="L30" s="20"/>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
-        <v>77.1563906637323</v>
+        <v>80.3712402747212</v>
       </c>
       <c r="C31" s="1" t="str">
         <f aca="false">IF($B$10&gt;L21,"","Discount rate must exceed terminal growth")</f>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
-        <v>38.8142762926079</v>
+        <v>41.4458015215345</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
-        <v>27.9167516744334</v>
+        <v>30.958024030403</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
-        <v>135.17044339531</v>
+        <v>149.896015253973</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
-        <v>-0.545805872228927</v>
+        <v>-0.496325615315694</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,43 +2352,43 @@
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.964485644340824</v>
+        <v>0.965744177733016</v>
       </c>
       <c r="C47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.897195948224023</v>
+        <v>0.900712719392852</v>
       </c>
       <c r="D47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.834600882068858</v>
+        <v>0.840060361306521</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.776372913552426</v>
+        <v>0.78349222281899</v>
       </c>
       <c r="F47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.722207361444118</v>
+        <v>0.730733280002789</v>
       </c>
       <c r="G47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.671820801343365</v>
+        <v>0.681527028542053</v>
       </c>
       <c r="H47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.624949582644991</v>
+        <v>0.635634236655524</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.581348448972085</v>
+        <v>0.592831781995452</v>
       </c>
       <c r="J47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.540789254857753</v>
+        <v>0.55291156686761</v>
       </c>
       <c r="K47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.503059771960701</v>
+        <v>0.515679506498424</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,43 +2397,43 @@
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
-        <v>3.93151354231362</v>
+        <v>3.93664367680954</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">C46*C47</f>
-        <v>4.06548194410648</v>
+        <v>4.08141755963922</v>
       </c>
       <c r="D48" s="20" t="n">
         <f aca="false">D46*D47</f>
-        <v>4.39697790305629</v>
+        <v>4.42574040509282</v>
       </c>
       <c r="E48" s="20" t="n">
         <f aca="false">E46*E47</f>
-        <v>4.73450835634195</v>
+        <v>4.77792361288368</v>
       </c>
       <c r="F48" s="20" t="n">
         <f aca="false">F46*F47</f>
-        <v>4.83743157183607</v>
+        <v>4.89453919745228</v>
       </c>
       <c r="G48" s="20" t="n">
         <f aca="false">G46*G47</f>
-        <v>4.65298427387797</v>
+        <v>4.72020893025043</v>
       </c>
       <c r="H48" s="20" t="n">
         <f aca="false">H46*H47</f>
-        <v>4.44387607539379</v>
+        <v>4.51985224955221</v>
       </c>
       <c r="I48" s="20" t="n">
         <f aca="false">I46*I47</f>
-        <v>4.21389363325606</v>
+        <v>4.29713036331234</v>
       </c>
       <c r="J48" s="20" t="n">
         <f aca="false">J46*J47</f>
-        <v>3.96710606954326</v>
+        <v>4.05603257301798</v>
       </c>
       <c r="K48" s="20" t="n">
         <f aca="false">K46*K47</f>
-        <v>3.70774339988118</v>
+        <v>3.80075568201642</v>
       </c>
       <c r="L48" s="20"/>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
-        <v>124.682319432656</v>
+        <v>130.785649754535</v>
       </c>
       <c r="C49" s="1" t="str">
         <f aca="false">IF($B$10&gt;L39,"","Discount rate must exceed terminal growth")</f>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
-        <v>62.7226591813234</v>
+        <v>67.4434793224942</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
-        <v>63.0041759509301</v>
+        <v>68.2837235725212</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
-        <v>305.060649546943</v>
+        <v>330.62375234843</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
-        <v>0.0250521649399122</v>
+        <v>0.110948244647871</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2931,43 +2931,43 @@
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.964485644340824</v>
+        <v>0.965744177733016</v>
       </c>
       <c r="C65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.897195948224023</v>
+        <v>0.900712719392852</v>
       </c>
       <c r="D65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.834600882068858</v>
+        <v>0.840060361306521</v>
       </c>
       <c r="E65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.776372913552426</v>
+        <v>0.78349222281899</v>
       </c>
       <c r="F65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.722207361444118</v>
+        <v>0.730733280002789</v>
       </c>
       <c r="G65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.671820801343365</v>
+        <v>0.681527028542053</v>
       </c>
       <c r="H65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.624949582644991</v>
+        <v>0.635634236655524</v>
       </c>
       <c r="I65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.581348448972085</v>
+        <v>0.592831781995452</v>
       </c>
       <c r="J65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.540789254857753</v>
+        <v>0.55291156686761</v>
       </c>
       <c r="K65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.503059771960701</v>
+        <v>0.515679506498424</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2976,43 +2976,43 @@
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
-        <v>3.99065580202459</v>
+        <v>3.99586310978813</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">C64*C65</f>
-        <v>4.25486206485761</v>
+        <v>4.27154000044866</v>
       </c>
       <c r="D66" s="20" t="n">
         <f aca="false">D64*D65</f>
-        <v>4.92147448138364</v>
+        <v>4.9536679385523</v>
       </c>
       <c r="E66" s="20" t="n">
         <f aca="false">E64*E65</f>
-        <v>5.37094781595569</v>
+        <v>5.42019919746177</v>
       </c>
       <c r="F66" s="20" t="n">
         <f aca="false">F64*F65</f>
-        <v>5.56041891723055</v>
+        <v>5.62606166939747</v>
       </c>
       <c r="G66" s="20" t="n">
         <f aca="false">G64*G65</f>
-        <v>5.43994292321079</v>
+        <v>5.51853727732277</v>
       </c>
       <c r="H66" s="20" t="n">
         <f aca="false">H64*H65</f>
-        <v>5.27494710239581</v>
+        <v>5.36513195294716</v>
       </c>
       <c r="I66" s="20" t="n">
         <f aca="false">I64*I65</f>
-        <v>5.06925605507176</v>
+        <v>5.16938869594152</v>
       </c>
       <c r="J66" s="20" t="n">
         <f aca="false">J64*J65</f>
-        <v>4.82766912510041</v>
+        <v>4.93588597831843</v>
       </c>
       <c r="K66" s="20" t="n">
         <f aca="false">K64*K65</f>
-        <v>4.55577291422759</v>
+        <v>4.67005882615337</v>
       </c>
       <c r="L66" s="20"/>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
-        <v>167.949981710764</v>
+        <v>176.958792990269</v>
       </c>
       <c r="C67" s="1" t="str">
         <f aca="false">IF($B$10&gt;L57,"","Discount rate must exceed terminal growth")</f>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
-        <v>84.4888795002209</v>
+        <v>91.2540230397786</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
-        <v>91.0848267016793</v>
+        <v>98.5103576861102</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
-        <v>441.024677778915</v>
+        <v>476.978442289789</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
-        <v>0.481912863624317</v>
+        <v>0.602723214629423</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3089,11 +3089,11 @@
       </c>
       <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
-        <v>135.17044339531</v>
+        <v>149.896015253973</v>
       </c>
       <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
-        <v>-0.545805872228927</v>
+        <v>-0.496325615315694</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3102,11 +3102,11 @@
       </c>
       <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
-        <v>305.060649546943</v>
+        <v>330.62375234843</v>
       </c>
       <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
-        <v>0.0250521649399122</v>
+        <v>0.110948244647871</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3115,11 +3115,11 @@
       </c>
       <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
-        <v>441.024677778915</v>
+        <v>476.978442289789</v>
       </c>
       <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
-        <v>0.481912863624317</v>
+        <v>0.602723214629423</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
-        <v>305.060649546943</v>
+        <v>330.62375234843</v>
       </c>
       <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
-        <v>0.0250521649399122</v>
+        <v>0.110948244647871</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
-        <v>0.593547653595603</v>
+        <v>0.607852329339917</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3347,7 +3347,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="14" t="n">
-        <v>0.0531</v>
+        <v>0.0503</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>93</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
-        <v>0.0964</v>
+        <v>0.0936</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>108</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
-        <v>0.0651</v>
+        <v>0.0623</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>110</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
-        <v>0.053382</v>
+        <v>0.051086</v>
       </c>
       <c r="C20" s="3"/>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
-        <v>0.0829464073175549</v>
+        <v>0.080304029957193</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>120</v>
@@ -3538,7 +3538,7 @@
         <v>121</v>
       </c>
       <c r="B26" s="31" t="n">
-        <v>0.075</v>
+        <v>0.0722</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>122</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
-        <v>0.075</v>
+        <v>0.0722</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>124</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
-        <v>0.075</v>
+        <v>0.0722</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>127</v>

--- a/models/holdings/LNG_Valuation.xlsx
+++ b/models/holdings/LNG_Valuation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
   <si>
     <t xml:space="preserve">Cheniere Energy (LNG): valuation summary</t>
   </si>
@@ -90,15 +90,12 @@
     <t xml:space="preserve">Share price ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Oct 23, 2026 intraday (Yahoo Finance via the site's price feed)</t>
+    <t xml:space="preserve">Oct 28, 2026 close (before Q3 results)</t>
   </si>
   <si>
     <t xml:space="preserve">Price date</t>
   </si>
   <si>
-    <t xml:space="preserve">Oct 23, 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Text</t>
   </si>
   <si>
@@ -141,7 +138,7 @@
     <t xml:space="preserve">Base-year revenue (2026E)</t>
   </si>
   <si>
-    <t xml:space="preserve">2026E consensus $22.6B (Stock Analysis). Revenue swings with gas prices; margin is the lever</t>
+    <t xml:space="preserve">2026E revenue about $24.3B: $17.77B for nine months plus about $6.5B in Q4 (Q3 2026 release, Oct 29). 2026 EBITDA guidance raised to $8.75B to $9.25B. Margin is the lever</t>
   </si>
   <si>
     <t xml:space="preserve">Selected scenario (1 Bear, 2 Base, 3 Bull)</t>
@@ -243,7 +240,7 @@
     <t xml:space="preserve">Value vs share price</t>
   </si>
   <si>
-    <t xml:space="preserve">Base: expansions come online, contracts hold</t>
+    <t xml:space="preserve">Base: 2027 near 2026 as spot margins normalize, trains 8 and 9 in 2028</t>
   </si>
   <si>
     <t xml:space="preserve">Bull: more trains sanctioned at good returns</t>
@@ -926,7 +923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
@@ -985,7 +982,7 @@
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">LNG!B4</f>
-        <v>297.605</v>
+        <v>297.77</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">LNG!B10</f>
@@ -993,27 +990,27 @@
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">LNG!B75</f>
-        <v>149.896015253973</v>
+        <v>181.632914629396</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">LNG!B76</f>
-        <v>330.62375234843</v>
+        <v>379.866227557491</v>
       </c>
       <c r="G5" s="5" t="n">
         <f aca="false">LNG!B77</f>
-        <v>476.978442289789</v>
+        <v>532.479526906825</v>
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
-        <v>0.110948244647871</v>
+        <v>0.275703487784165</v>
       </c>
       <c r="I5" s="6" t="n">
         <f aca="false">LNG!B86</f>
-        <v>0.0762688670296594</v>
+        <v>0.0819262899203144</v>
       </c>
       <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1026,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>305</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1034,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>440</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1042,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1059,12 +1056,6 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1105,7 +1096,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="10" t="n">
-        <v>297.605</v>
+        <v>297.77</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
@@ -1116,142 +1107,142 @@
         <v>23</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>0.20653</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>-22.27</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>-26.85</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>-15.82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0.18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
         <v>0.0722</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="E15" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="G15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="H15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="I15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="J15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="K15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="L15" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>0.5</v>
@@ -1295,7 +1286,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0</v>
@@ -1330,7 +1321,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -1346,87 +1337,87 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="13" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="G20" s="20" t="n">
         <f aca="false">F20*(1+$F21+($L21-$F21)*G$17/5)</f>
-        <v>24.3590555555556</v>
+        <v>24.8587826086957</v>
       </c>
       <c r="H20" s="20" t="n">
         <f aca="false">G20*(1+$F21+($L21-$F21)*H$17/5)</f>
-        <v>25.0573484814815</v>
+        <v>25.5569901550095</v>
       </c>
       <c r="I20" s="20" t="n">
         <f aca="false">H20*(1+$F21+($L21-$F21)*I$17/5)</f>
-        <v>25.57798449993</v>
+        <v>26.0781305194746</v>
       </c>
       <c r="J20" s="20" t="n">
         <f aca="false">I20*(1+$F21+($L21-$F21)*J$17/5)</f>
-        <v>25.9076563001514</v>
+        <v>26.4092093938958</v>
       </c>
       <c r="K20" s="20" t="n">
         <f aca="false">J20*(1+$F21+($L21-$F21)*K$17/5)</f>
-        <v>26.0371945816521</v>
+        <v>26.5412554408653</v>
       </c>
       <c r="L20" s="20" t="n">
         <f aca="false">K20*(1+L21)</f>
-        <v>26.1673805545604</v>
+        <v>26.6739617180696</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">B20/$B$12-1</f>
-        <v>-0.0707964601769913</v>
+        <v>-0.0740740740740741</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">C20/B20-1</f>
-        <v>-0.0238095238095238</v>
+        <v>-0.0444444444444444</v>
       </c>
       <c r="D21" s="7" t="n">
         <f aca="false">D20/C20-1</f>
-        <v>0.0487804878048781</v>
+        <v>0.0232558139534884</v>
       </c>
       <c r="E21" s="7" t="n">
         <f aca="false">E20/D20-1</f>
-        <v>0.0465116279069768</v>
+        <v>0.0454545454545454</v>
       </c>
       <c r="F21" s="7" t="n">
         <f aca="false">F20/E20-1</f>
-        <v>0.0444444444444445</v>
+        <v>0.0434782608695652</v>
       </c>
       <c r="G21" s="7" t="n">
         <f aca="false">G20/F20-1</f>
-        <v>0.0365555555555557</v>
+        <v>0.0357826086956521</v>
       </c>
       <c r="H21" s="7" t="n">
         <f aca="false">H20/G20-1</f>
-        <v>0.0286666666666666</v>
+        <v>0.0280869565217392</v>
       </c>
       <c r="I21" s="7" t="n">
         <f aca="false">I20/H20-1</f>
-        <v>0.0207777777777778</v>
+        <v>0.0203913043478261</v>
       </c>
       <c r="J21" s="7" t="n">
         <f aca="false">J20/I20-1</f>
-        <v>0.012888888888889</v>
+        <v>0.012695652173913</v>
       </c>
       <c r="K21" s="7" t="n">
         <f aca="false">K20/J20-1</f>
@@ -1438,7 +1429,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>0.29</v>
@@ -1481,105 +1472,105 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">B20*B22</f>
-        <v>6.09</v>
+        <v>6.525</v>
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">C20*C22</f>
-        <v>5.74</v>
+        <v>6.02</v>
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">D20*D22</f>
-        <v>6.02</v>
+        <v>6.16</v>
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">E20*E22</f>
-        <v>6.3</v>
+        <v>6.44</v>
       </c>
       <c r="F23" s="20" t="n">
         <f aca="false">F20*F22</f>
-        <v>6.58</v>
+        <v>6.72</v>
       </c>
       <c r="G23" s="20" t="n">
         <f aca="false">G20*G22</f>
-        <v>6.77181744444445</v>
+        <v>6.91074156521739</v>
       </c>
       <c r="H23" s="20" t="n">
         <f aca="false">H20*H22</f>
-        <v>6.91582818088889</v>
+        <v>7.05372928278261</v>
       </c>
       <c r="I23" s="20" t="n">
         <f aca="false">I20*I22</f>
-        <v>7.00836775298083</v>
+        <v>7.14540776233605</v>
       </c>
       <c r="J23" s="20" t="n">
         <f aca="false">J20*J22</f>
-        <v>7.04688251364117</v>
+        <v>7.18330495513966</v>
       </c>
       <c r="K23" s="20" t="n">
         <f aca="false">K20*K22</f>
-        <v>7.03004253704607</v>
+        <v>7.16613896903363</v>
       </c>
       <c r="L23" s="20" t="n">
         <f aca="false">L20*L22</f>
-        <v>7.0651927497313</v>
+        <v>7.20196966387879</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">B23*(1-$B$9)</f>
-        <v>4.9938</v>
+        <v>5.3505</v>
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">C23*(1-$B$9)</f>
-        <v>4.7068</v>
+        <v>4.9364</v>
       </c>
       <c r="D24" s="20" t="n">
         <f aca="false">D23*(1-$B$9)</f>
-        <v>4.9364</v>
+        <v>5.0512</v>
       </c>
       <c r="E24" s="20" t="n">
         <f aca="false">E23*(1-$B$9)</f>
-        <v>5.166</v>
+        <v>5.2808</v>
       </c>
       <c r="F24" s="20" t="n">
         <f aca="false">F23*(1-$B$9)</f>
-        <v>5.3956</v>
+        <v>5.5104</v>
       </c>
       <c r="G24" s="20" t="n">
         <f aca="false">G23*(1-$B$9)</f>
-        <v>5.55289030444445</v>
+        <v>5.66680808347826</v>
       </c>
       <c r="H24" s="20" t="n">
         <f aca="false">H23*(1-$B$9)</f>
-        <v>5.67097910832889</v>
+        <v>5.78405801188174</v>
       </c>
       <c r="I24" s="20" t="n">
         <f aca="false">I23*(1-$B$9)</f>
-        <v>5.74686155744428</v>
+        <v>5.85923436511556</v>
       </c>
       <c r="J24" s="20" t="n">
         <f aca="false">J23*(1-$B$9)</f>
-        <v>5.77844366118576</v>
+        <v>5.89031006321452</v>
       </c>
       <c r="K24" s="20" t="n">
         <f aca="false">K23*(1-$B$9)</f>
-        <v>5.76463488037778</v>
+        <v>5.87623395460757</v>
       </c>
       <c r="L24" s="20" t="n">
         <f aca="false">L23*(1-$B$9)</f>
-        <v>5.79345805477967</v>
+        <v>5.90561512438061</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" s="22" t="n">
         <v>0.08</v>
@@ -1622,56 +1613,56 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="20" t="n">
         <f aca="false">B20*B25</f>
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="C26" s="20" t="n">
         <f aca="false">C20*C25</f>
-        <v>1.435</v>
+        <v>1.505</v>
       </c>
       <c r="D26" s="20" t="n">
         <f aca="false">D20*D25</f>
-        <v>1.075</v>
+        <v>1.1</v>
       </c>
       <c r="E26" s="20" t="n">
         <f aca="false">E20*E25</f>
-        <v>0.675</v>
+        <v>0.69</v>
       </c>
       <c r="F26" s="20" t="n">
         <f aca="false">F20*F25</f>
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G26" s="20" t="n">
         <f aca="false">G20*G25</f>
-        <v>0.462822055555556</v>
+        <v>0.472316869565217</v>
       </c>
       <c r="H26" s="20" t="n">
         <f aca="false">H20*H25</f>
-        <v>0.451032272666667</v>
+        <v>0.46002582279017</v>
       </c>
       <c r="I26" s="20" t="n">
         <f aca="false">I20*I25</f>
-        <v>0.434825736498811</v>
+        <v>0.443328218831069</v>
       </c>
       <c r="J26" s="20" t="n">
         <f aca="false">J20*J25</f>
-        <v>0.414522500802422</v>
+        <v>0.422547350302333</v>
       </c>
       <c r="K26" s="20" t="n">
         <f aca="false">K20*K25</f>
-        <v>0.390557918724782</v>
+        <v>0.398118831612979</v>
       </c>
       <c r="L26" s="20" t="n">
         <f aca="false">L20*L25</f>
-        <v>0.392510708318406</v>
+        <v>0.400109425771044</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="20" t="n">
         <f aca="false">$B$11*(B20-$B$12)</f>
@@ -1720,56 +1711,56 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="20" t="n">
         <f aca="false">B24-B26-B27</f>
-        <v>3.3138</v>
+        <v>3.5505</v>
       </c>
       <c r="C28" s="20" t="n">
         <f aca="false">C24-C26-C27</f>
-        <v>3.2718</v>
+        <v>3.4314</v>
       </c>
       <c r="D28" s="20" t="n">
         <f aca="false">D24-D26-D27</f>
-        <v>3.8614</v>
+        <v>3.9512</v>
       </c>
       <c r="E28" s="20" t="n">
         <f aca="false">E24-E26-E27</f>
-        <v>4.491</v>
+        <v>4.5908</v>
       </c>
       <c r="F28" s="20" t="n">
         <f aca="false">F24-F26-F27</f>
-        <v>4.9256</v>
+        <v>5.0304</v>
       </c>
       <c r="G28" s="20" t="n">
         <f aca="false">G24-G26-G27</f>
-        <v>5.09006824888889</v>
+        <v>5.19449121391304</v>
       </c>
       <c r="H28" s="20" t="n">
         <f aca="false">H24-H26-H27</f>
-        <v>5.21994683566222</v>
+        <v>5.32403218909157</v>
       </c>
       <c r="I28" s="20" t="n">
         <f aca="false">I24-I26-I27</f>
-        <v>5.31203582094547</v>
+        <v>5.4159061462845</v>
       </c>
       <c r="J28" s="20" t="n">
         <f aca="false">J24-J26-J27</f>
-        <v>5.36392116038334</v>
+        <v>5.46776271291219</v>
       </c>
       <c r="K28" s="20" t="n">
         <f aca="false">K24-K26-K27</f>
-        <v>5.374076961653</v>
+        <v>5.47811512299459</v>
       </c>
       <c r="L28" s="20" t="n">
         <f aca="false">L24-L26-L27</f>
-        <v>5.40094734646126</v>
+        <v>5.50550569860957</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -1814,57 +1805,57 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
-        <v>3.20028305617167</v>
+        <v>3.42887470304107</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">C28*C29</f>
-        <v>2.94695187530953</v>
+        <v>3.09070562532463</v>
       </c>
       <c r="D30" s="20" t="n">
         <f aca="false">D28*D29</f>
-        <v>3.243809079149</v>
+        <v>3.31924649959433</v>
       </c>
       <c r="E30" s="20" t="n">
         <f aca="false">E28*E29</f>
-        <v>3.51866357268009</v>
+        <v>3.59685609651742</v>
       </c>
       <c r="F30" s="20" t="n">
         <f aca="false">F28*F29</f>
-        <v>3.59929984398174</v>
+        <v>3.67588069172603</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">G28*G29</f>
-        <v>3.46901908874149</v>
+        <v>3.54018616180596</v>
       </c>
       <c r="H30" s="20" t="n">
         <f aca="false">H28*H29</f>
-        <v>3.31797692226857</v>
+        <v>3.38413713644266</v>
       </c>
       <c r="I30" s="20" t="n">
         <f aca="false">I28*I29</f>
-        <v>3.14914366175478</v>
+        <v>3.21072129182196</v>
       </c>
       <c r="J30" s="20" t="n">
         <f aca="false">J28*J29</f>
-        <v>2.96577405334188</v>
+        <v>3.02318924885657</v>
       </c>
       <c r="K30" s="20" t="n">
         <f aca="false">K28*K29</f>
-        <v>2.77130135546977</v>
+        <v>2.82495170316741</v>
       </c>
       <c r="L30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
-        <v>80.3712402747212</v>
+        <v>81.9271681340709</v>
       </c>
       <c r="C31" s="1" t="str">
         <f aca="false">IF($B$10&gt;L21,"","Discount rate must exceed terminal growth")</f>
@@ -1873,43 +1864,43 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
-        <v>41.4458015215345</v>
+        <v>42.2481616321911</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
-        <v>30.958024030403</v>
+        <v>37.2529107904892</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
-        <v>149.896015253973</v>
+        <v>181.632914629396</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
-        <v>-0.496325615315694</v>
+        <v>-0.390022787287517</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -1925,87 +1916,87 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="13" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
       <c r="G38" s="20" t="n">
         <f aca="false">F38*(1+$F39+($L39-$F39)*G$17/5)</f>
-        <v>29.8634470588235</v>
+        <v>31.2648251748252</v>
       </c>
       <c r="H38" s="20" t="n">
         <f aca="false">G38*(1+$F39+($L39-$F39)*H$17/5)</f>
-        <v>30.9648812532872</v>
+        <v>32.3706817184214</v>
       </c>
       <c r="I38" s="20" t="n">
         <f aca="false">H38*(1+$F39+($L39-$F39)*I$17/5)</f>
-        <v>31.8810774456639</v>
+        <v>33.2958493840381</v>
       </c>
       <c r="J38" s="20" t="n">
         <f aca="false">I38*(1+$F39+($L39-$F39)*J$17/5)</f>
-        <v>32.5918379369525</v>
+        <v>34.0213729272596</v>
       </c>
       <c r="K38" s="20" t="n">
         <f aca="false">J38*(1+$F39+($L39-$F39)*K$17/5)</f>
-        <v>33.0807155060068</v>
+        <v>34.5316935211685</v>
       </c>
       <c r="L38" s="20" t="n">
         <f aca="false">K38*(1+L39)</f>
-        <v>33.5769262385969</v>
+        <v>35.049668923986</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="7" t="n">
         <f aca="false">B38/$B$12-1</f>
-        <v>0.0353982300884954</v>
+        <v>0.0123456790123457</v>
       </c>
       <c r="C39" s="7" t="n">
         <f aca="false">C38/B38-1</f>
-        <v>0.0512820512820513</v>
+        <v>0.0487804878048781</v>
       </c>
       <c r="D39" s="7" t="n">
         <f aca="false">D38/C38-1</f>
-        <v>0.0487804878048781</v>
+        <v>0.0542635658914727</v>
       </c>
       <c r="E39" s="7" t="n">
         <f aca="false">E38/D38-1</f>
-        <v>0.0542635658914727</v>
+        <v>0.0514705882352942</v>
       </c>
       <c r="F39" s="7" t="n">
         <f aca="false">F38/E38-1</f>
-        <v>0.0514705882352942</v>
+        <v>0.048951048951049</v>
       </c>
       <c r="G39" s="7" t="n">
         <f aca="false">G38/F38-1</f>
-        <v>0.0441764705882353</v>
+        <v>0.0421608391608392</v>
       </c>
       <c r="H39" s="7" t="n">
         <f aca="false">H38/G38-1</f>
-        <v>0.0368823529411766</v>
+        <v>0.0353706293706293</v>
       </c>
       <c r="I39" s="7" t="n">
         <f aca="false">I38/H38-1</f>
-        <v>0.0295882352941177</v>
+        <v>0.0285804195804196</v>
       </c>
       <c r="J39" s="7" t="n">
         <f aca="false">J38/I38-1</f>
-        <v>0.0222941176470588</v>
+        <v>0.0217902097902098</v>
       </c>
       <c r="K39" s="7" t="n">
         <f aca="false">K38/J38-1</f>
@@ -2017,7 +2008,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.31</v>
@@ -2060,105 +2051,105 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">B38*B40</f>
-        <v>7.254</v>
+        <v>7.626</v>
       </c>
       <c r="C41" s="20" t="n">
         <f aca="false">C38*C40</f>
-        <v>7.626</v>
+        <v>7.998</v>
       </c>
       <c r="D41" s="20" t="n">
         <f aca="false">D38*D40</f>
-        <v>7.998</v>
+        <v>8.432</v>
       </c>
       <c r="E41" s="20" t="n">
         <f aca="false">E38*E40</f>
-        <v>8.432</v>
+        <v>8.866</v>
       </c>
       <c r="F41" s="20" t="n">
         <f aca="false">F38*F40</f>
-        <v>8.866</v>
+        <v>9.3</v>
       </c>
       <c r="G41" s="20" t="n">
         <f aca="false">G38*G40</f>
-        <v>9.1382148</v>
+        <v>9.5670365034965</v>
       </c>
       <c r="H41" s="20" t="n">
         <f aca="false">H38*H40</f>
-        <v>9.35139413849274</v>
+        <v>9.77594587896327</v>
       </c>
       <c r="I41" s="20" t="n">
         <f aca="false">I38*I40</f>
-        <v>9.50056107880784</v>
+        <v>9.92216311644337</v>
       </c>
       <c r="J41" s="20" t="n">
         <f aca="false">J38*J40</f>
-        <v>9.58200035346404</v>
+        <v>10.0022836406143</v>
       </c>
       <c r="K41" s="20" t="n">
         <f aca="false">K38*K40</f>
-        <v>9.59340749674197</v>
+        <v>10.0141911211389</v>
       </c>
       <c r="L41" s="20" t="n">
         <f aca="false">L38*L40</f>
-        <v>9.7373086091931</v>
+        <v>10.1644039879559</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="20" t="n">
         <f aca="false">B41*(1-$B$9)</f>
-        <v>5.94828</v>
+        <v>6.25332</v>
       </c>
       <c r="C42" s="20" t="n">
         <f aca="false">C41*(1-$B$9)</f>
-        <v>6.25332</v>
+        <v>6.55836</v>
       </c>
       <c r="D42" s="20" t="n">
         <f aca="false">D41*(1-$B$9)</f>
-        <v>6.55836</v>
+        <v>6.91424</v>
       </c>
       <c r="E42" s="20" t="n">
         <f aca="false">E41*(1-$B$9)</f>
-        <v>6.91424</v>
+        <v>7.27012</v>
       </c>
       <c r="F42" s="20" t="n">
         <f aca="false">F41*(1-$B$9)</f>
-        <v>7.27012</v>
+        <v>7.626</v>
       </c>
       <c r="G42" s="20" t="n">
         <f aca="false">G41*(1-$B$9)</f>
-        <v>7.493336136</v>
+        <v>7.84496993286713</v>
       </c>
       <c r="H42" s="20" t="n">
         <f aca="false">H41*(1-$B$9)</f>
-        <v>7.66814319356404</v>
+        <v>8.01627562074989</v>
       </c>
       <c r="I42" s="20" t="n">
         <f aca="false">I41*(1-$B$9)</f>
-        <v>7.79046008462243</v>
+        <v>8.13617375548356</v>
       </c>
       <c r="J42" s="20" t="n">
         <f aca="false">J41*(1-$B$9)</f>
-        <v>7.85724028984051</v>
+        <v>8.20187258530373</v>
       </c>
       <c r="K42" s="20" t="n">
         <f aca="false">K41*(1-$B$9)</f>
-        <v>7.86659414732841</v>
+        <v>8.21163671933386</v>
       </c>
       <c r="L42" s="20" t="n">
         <f aca="false">L41*(1-$B$9)</f>
-        <v>7.98459305953834</v>
+        <v>8.33481127012387</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.08</v>
@@ -2201,56 +2192,56 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">B38*B43</f>
-        <v>1.872</v>
+        <v>1.968</v>
       </c>
       <c r="C44" s="20" t="n">
         <f aca="false">C38*C43</f>
-        <v>1.722</v>
+        <v>1.806</v>
       </c>
       <c r="D44" s="20" t="n">
         <f aca="false">D38*D43</f>
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="E44" s="20" t="n">
         <f aca="false">E38*E43</f>
-        <v>0.816</v>
+        <v>0.858</v>
       </c>
       <c r="F44" s="20" t="n">
         <f aca="false">F38*F43</f>
-        <v>0.572</v>
+        <v>0.6</v>
       </c>
       <c r="G44" s="20" t="n">
         <f aca="false">G38*G43</f>
-        <v>0.567405494117647</v>
+        <v>0.594031678321678</v>
       </c>
       <c r="H44" s="20" t="n">
         <f aca="false">H38*H43</f>
-        <v>0.55736786255917</v>
+        <v>0.582672270931586</v>
       </c>
       <c r="I44" s="20" t="n">
         <f aca="false">I38*I43</f>
-        <v>0.541978316576286</v>
+        <v>0.566029439528649</v>
       </c>
       <c r="J44" s="20" t="n">
         <f aca="false">J38*J43</f>
-        <v>0.52146940699124</v>
+        <v>0.544341966836153</v>
       </c>
       <c r="K44" s="20" t="n">
         <f aca="false">K38*K43</f>
-        <v>0.496210732590102</v>
+        <v>0.517975402817527</v>
       </c>
       <c r="L44" s="20" t="n">
         <f aca="false">L38*L43</f>
-        <v>0.503653893578953</v>
+        <v>0.52574503385979</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="20" t="n">
         <f aca="false">$B$11*(B38-$B$12)</f>
@@ -2299,56 +2290,56 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="20" t="n">
         <f aca="false">B42-B44-B45</f>
-        <v>4.07628</v>
+        <v>4.28532</v>
       </c>
       <c r="C46" s="20" t="n">
         <f aca="false">C42-C44-C45</f>
-        <v>4.53132</v>
+        <v>4.75236</v>
       </c>
       <c r="D46" s="20" t="n">
         <f aca="false">D42-D44-D45</f>
-        <v>5.26836</v>
+        <v>5.55424</v>
       </c>
       <c r="E46" s="20" t="n">
         <f aca="false">E42-E44-E45</f>
-        <v>6.09824</v>
+        <v>6.41212</v>
       </c>
       <c r="F46" s="20" t="n">
         <f aca="false">F42-F44-F45</f>
-        <v>6.69812</v>
+        <v>7.026</v>
       </c>
       <c r="G46" s="20" t="n">
         <f aca="false">G42-G44-G45</f>
-        <v>6.92593064188235</v>
+        <v>7.25093825454546</v>
       </c>
       <c r="H46" s="20" t="n">
         <f aca="false">H42-H44-H45</f>
-        <v>7.11077533100487</v>
+        <v>7.4336033498183</v>
       </c>
       <c r="I46" s="20" t="n">
         <f aca="false">I42-I44-I45</f>
-        <v>7.24848176804614</v>
+        <v>7.57014431595491</v>
       </c>
       <c r="J46" s="20" t="n">
         <f aca="false">J42-J44-J45</f>
-        <v>7.33577088284927</v>
+        <v>7.65753061846758</v>
       </c>
       <c r="K46" s="20" t="n">
         <f aca="false">K42-K44-K45</f>
-        <v>7.37038341473831</v>
+        <v>7.69366131651633</v>
       </c>
       <c r="L46" s="20" t="n">
         <f aca="false">L42-L44-L45</f>
-        <v>7.48093916595939</v>
+        <v>7.80906623626408</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2393,57 +2384,57 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
-        <v>3.93664367680954</v>
+        <v>4.13852283972285</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">C46*C47</f>
-        <v>4.08141755963922</v>
+        <v>4.28051109913382</v>
       </c>
       <c r="D48" s="20" t="n">
         <f aca="false">D46*D47</f>
-        <v>4.42574040509282</v>
+        <v>4.66589686118313</v>
       </c>
       <c r="E48" s="20" t="n">
         <f aca="false">E46*E47</f>
-        <v>4.77792361288368</v>
+        <v>5.0238461517821</v>
       </c>
       <c r="F48" s="20" t="n">
         <f aca="false">F46*F47</f>
-        <v>4.89453919745228</v>
+        <v>5.1341320252996</v>
       </c>
       <c r="G48" s="20" t="n">
         <f aca="false">G46*G47</f>
-        <v>4.72020893025043</v>
+        <v>4.94171040276226</v>
       </c>
       <c r="H48" s="20" t="n">
         <f aca="false">H46*H47</f>
-        <v>4.51985224955221</v>
+        <v>4.7250527908617</v>
       </c>
       <c r="I48" s="20" t="n">
         <f aca="false">I46*I47</f>
-        <v>4.29713036331234</v>
+        <v>4.48782214479029</v>
       </c>
       <c r="J48" s="20" t="n">
         <f aca="false">J46*J47</f>
-        <v>4.05603257301798</v>
+        <v>4.23393725259361</v>
       </c>
       <c r="K48" s="20" t="n">
         <f aca="false">K46*K47</f>
-        <v>3.80075568201642</v>
+        <v>3.96746347086716</v>
       </c>
       <c r="L48" s="20"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
-        <v>130.785649754535</v>
+        <v>136.522136997624</v>
       </c>
       <c r="C49" s="1" t="str">
         <f aca="false">IF($B$10&gt;L39,"","Discount rate must exceed terminal growth")</f>
@@ -2452,43 +2443,43 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
-        <v>67.4434793224942</v>
+        <v>70.4016682330448</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
-        <v>68.2837235725212</v>
+        <v>77.9105632720414</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
-        <v>330.62375234843</v>
+        <v>379.866227557491</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
-        <v>0.110948244647871</v>
+        <v>0.275703487784165</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -2504,87 +2495,87 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="13" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="G56" s="20" t="n">
         <f aca="false">F56*(1+$F57+($L57-$F57)*G$17/5)</f>
-        <v>33.8346666666667</v>
+        <v>35.3355873015873</v>
       </c>
       <c r="H56" s="20" t="n">
         <f aca="false">G56*(1+$F57+($L57-$F57)*H$17/5)</f>
-        <v>35.4587306666667</v>
+        <v>36.9643896114891</v>
       </c>
       <c r="I56" s="20" t="n">
         <f aca="false">H56*(1+$F57+($L57-$F57)*I$17/5)</f>
-        <v>36.8298015857778</v>
+        <v>38.3467404356901</v>
       </c>
       <c r="J56" s="20" t="n">
         <f aca="false">I56*(1+$F57+($L57-$F57)*J$17/5)</f>
-        <v>37.9101424322939</v>
+        <v>39.4472310183525</v>
       </c>
       <c r="K56" s="20" t="n">
         <f aca="false">J56*(1+$F57+($L57-$F57)*K$17/5)</f>
-        <v>38.6683452809398</v>
+        <v>40.2361756387195</v>
       </c>
       <c r="L56" s="20" t="n">
         <f aca="false">K56*(1+L57)</f>
-        <v>39.4417121865586</v>
+        <v>41.0408991514939</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="7" t="n">
         <f aca="false">B56/$B$12-1</f>
-        <v>0.0619469026548671</v>
+        <v>0.0617283950617285</v>
       </c>
       <c r="C57" s="7" t="n">
         <f aca="false">C56/B56-1</f>
-        <v>0.0833333333333333</v>
+        <v>0.065891472868217</v>
       </c>
       <c r="D57" s="7" t="n">
         <f aca="false">D56/C56-1</f>
-        <v>0.0769230769230769</v>
+        <v>0.0727272727272728</v>
       </c>
       <c r="E57" s="7" t="n">
         <f aca="false">E56/D56-1</f>
-        <v>0.0714285714285714</v>
+        <v>0.0677966101694916</v>
       </c>
       <c r="F57" s="7" t="n">
         <f aca="false">F56/E56-1</f>
-        <v>0.0666666666666667</v>
+        <v>0.0634920634920635</v>
       </c>
       <c r="G57" s="7" t="n">
         <f aca="false">G56/F56-1</f>
-        <v>0.0573333333333332</v>
+        <v>0.0547936507936508</v>
       </c>
       <c r="H57" s="7" t="n">
         <f aca="false">H56/G56-1</f>
-        <v>0.048</v>
+        <v>0.0460952380952382</v>
       </c>
       <c r="I57" s="7" t="n">
         <f aca="false">I56/H56-1</f>
-        <v>0.0386666666666666</v>
+        <v>0.0373968253968253</v>
       </c>
       <c r="J57" s="7" t="n">
         <f aca="false">J56/I56-1</f>
-        <v>0.0293333333333334</v>
+        <v>0.0286984126984127</v>
       </c>
       <c r="K57" s="7" t="n">
         <f aca="false">K56/J56-1</f>
@@ -2596,7 +2587,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="22" t="n">
         <v>0.32</v>
@@ -2639,105 +2630,105 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="20" t="n">
         <f aca="false">B56*B58</f>
-        <v>7.68</v>
+        <v>8.256</v>
       </c>
       <c r="C59" s="20" t="n">
         <f aca="false">C56*C58</f>
-        <v>8.32</v>
+        <v>8.8</v>
       </c>
       <c r="D59" s="20" t="n">
         <f aca="false">D56*D58</f>
-        <v>9.24</v>
+        <v>9.735</v>
       </c>
       <c r="E59" s="20" t="n">
         <f aca="false">E56*E58</f>
-        <v>9.9</v>
+        <v>10.395</v>
       </c>
       <c r="F59" s="20" t="n">
         <f aca="false">F56*F58</f>
-        <v>10.56</v>
+        <v>11.055</v>
       </c>
       <c r="G59" s="20" t="n">
         <f aca="false">G56*G58</f>
-        <v>11.0301013333333</v>
+        <v>11.5194014603175</v>
       </c>
       <c r="H59" s="20" t="n">
         <f aca="false">H56*H58</f>
-        <v>11.4177112746667</v>
+        <v>11.9025334548995</v>
       </c>
       <c r="I59" s="20" t="n">
         <f aca="false">I56*I58</f>
-        <v>11.7118769042773</v>
+        <v>12.1942634585495</v>
       </c>
       <c r="J59" s="20" t="n">
         <f aca="false">J56*J58</f>
-        <v>11.9037847237403</v>
+        <v>12.3864305397627</v>
       </c>
       <c r="K59" s="20" t="n">
         <f aca="false">K56*K58</f>
-        <v>11.9871870370913</v>
+        <v>12.4732144480031</v>
       </c>
       <c r="L59" s="20" t="n">
         <f aca="false">L56*L58</f>
-        <v>12.2269307778332</v>
+        <v>12.7226787369631</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" s="20" t="n">
         <f aca="false">B59*(1-$B$9)</f>
-        <v>6.2976</v>
+        <v>6.76992</v>
       </c>
       <c r="C60" s="20" t="n">
         <f aca="false">C59*(1-$B$9)</f>
-        <v>6.8224</v>
+        <v>7.216</v>
       </c>
       <c r="D60" s="20" t="n">
         <f aca="false">D59*(1-$B$9)</f>
-        <v>7.5768</v>
+        <v>7.9827</v>
       </c>
       <c r="E60" s="20" t="n">
         <f aca="false">E59*(1-$B$9)</f>
-        <v>8.118</v>
+        <v>8.5239</v>
       </c>
       <c r="F60" s="20" t="n">
         <f aca="false">F59*(1-$B$9)</f>
-        <v>8.6592</v>
+        <v>9.0651</v>
       </c>
       <c r="G60" s="20" t="n">
         <f aca="false">G59*(1-$B$9)</f>
-        <v>9.04468309333333</v>
+        <v>9.44590919746032</v>
       </c>
       <c r="H60" s="20" t="n">
         <f aca="false">H59*(1-$B$9)</f>
-        <v>9.36252324522667</v>
+        <v>9.76007743301757</v>
       </c>
       <c r="I60" s="20" t="n">
         <f aca="false">I59*(1-$B$9)</f>
-        <v>9.60373906150742</v>
+        <v>9.99929603601056</v>
       </c>
       <c r="J60" s="20" t="n">
         <f aca="false">J59*(1-$B$9)</f>
-        <v>9.76110347346704</v>
+        <v>10.1568730426054</v>
       </c>
       <c r="K60" s="20" t="n">
         <f aca="false">K59*(1-$B$9)</f>
-        <v>9.8294933704149</v>
+        <v>10.2280358473625</v>
       </c>
       <c r="L60" s="20" t="n">
         <f aca="false">L59*(1-$B$9)</f>
-        <v>10.0260832378232</v>
+        <v>10.4325965643098</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" s="22" t="n">
         <v>0.09</v>
@@ -2780,56 +2771,56 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="20" t="n">
         <f aca="false">B56*B61</f>
-        <v>2.16</v>
+        <v>2.322</v>
       </c>
       <c r="C62" s="20" t="n">
         <f aca="false">C56*C61</f>
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="D62" s="20" t="n">
         <f aca="false">D56*D61</f>
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="E62" s="20" t="n">
         <f aca="false">E56*E61</f>
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="F62" s="20" t="n">
         <f aca="false">F56*F61</f>
-        <v>0.96</v>
+        <v>1.005</v>
       </c>
       <c r="G62" s="20" t="n">
         <f aca="false">G56*G61</f>
-        <v>0.947370666666667</v>
+        <v>0.989396444444445</v>
       </c>
       <c r="H62" s="20" t="n">
         <f aca="false">H56*H61</f>
-        <v>0.921926997333333</v>
+        <v>0.961074129898715</v>
       </c>
       <c r="I62" s="20" t="n">
         <f aca="false">I56*I61</f>
-        <v>0.883915238058667</v>
+        <v>0.920321770456563</v>
       </c>
       <c r="J62" s="20" t="n">
         <f aca="false">J56*J61</f>
-        <v>0.834023133510466</v>
+        <v>0.867839082403754</v>
       </c>
       <c r="K62" s="20" t="n">
         <f aca="false">K56*K61</f>
-        <v>0.773366905618796</v>
+        <v>0.80472351277439</v>
       </c>
       <c r="L62" s="20" t="n">
         <f aca="false">L56*L61</f>
-        <v>0.788834243731172</v>
+        <v>0.820817983029878</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="20" t="n">
         <f aca="false">$B$11*(B56-$B$12)</f>
@@ -2878,56 +2869,56 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="20" t="n">
         <f aca="false">B60-B62-B63</f>
-        <v>4.1376</v>
+        <v>4.44792</v>
       </c>
       <c r="C64" s="20" t="n">
         <f aca="false">C60-C62-C63</f>
-        <v>4.7424</v>
+        <v>5.016</v>
       </c>
       <c r="D64" s="20" t="n">
         <f aca="false">D60-D62-D63</f>
-        <v>5.8968</v>
+        <v>6.2127</v>
       </c>
       <c r="E64" s="20" t="n">
         <f aca="false">E60-E62-E63</f>
-        <v>6.918</v>
+        <v>7.2639</v>
       </c>
       <c r="F64" s="20" t="n">
         <f aca="false">F60-F62-F63</f>
-        <v>7.6992</v>
+        <v>8.0601</v>
       </c>
       <c r="G64" s="20" t="n">
         <f aca="false">G60-G62-G63</f>
-        <v>8.09731242666667</v>
+        <v>8.45651275301587</v>
       </c>
       <c r="H64" s="20" t="n">
         <f aca="false">H60-H62-H63</f>
-        <v>8.44059624789333</v>
+        <v>8.79900330311885</v>
       </c>
       <c r="I64" s="20" t="n">
         <f aca="false">I60-I62-I63</f>
-        <v>8.71982382344875</v>
+        <v>9.078974265554</v>
       </c>
       <c r="J64" s="20" t="n">
         <f aca="false">J60-J62-J63</f>
-        <v>8.92708033995658</v>
+        <v>9.28903396020164</v>
       </c>
       <c r="K64" s="20" t="n">
         <f aca="false">K60-K62-K63</f>
-        <v>9.05612646479611</v>
+        <v>9.42331233458811</v>
       </c>
       <c r="L64" s="20" t="n">
         <f aca="false">L60-L62-L63</f>
-        <v>9.23724899409203</v>
+        <v>9.61177858127988</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2972,57 +2963,57 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
-        <v>3.99586310978813</v>
+        <v>4.29555284302224</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">C64*C65</f>
-        <v>4.27154000044866</v>
+        <v>4.51797500047455</v>
       </c>
       <c r="D66" s="20" t="n">
         <f aca="false">D64*D65</f>
-        <v>4.9536679385523</v>
+        <v>5.21904300668903</v>
       </c>
       <c r="E66" s="20" t="n">
         <f aca="false">E64*E65</f>
-        <v>5.42019919746177</v>
+        <v>5.69120915733486</v>
       </c>
       <c r="F66" s="20" t="n">
         <f aca="false">F64*F65</f>
-        <v>5.62606166939747</v>
+        <v>5.88978331015048</v>
       </c>
       <c r="G66" s="20" t="n">
         <f aca="false">G64*G65</f>
-        <v>5.51853727732277</v>
+        <v>5.76334200839088</v>
       </c>
       <c r="H66" s="20" t="n">
         <f aca="false">H64*H65</f>
-        <v>5.36513195294716</v>
+        <v>5.59294774790738</v>
       </c>
       <c r="I66" s="20" t="n">
         <f aca="false">I64*I65</f>
-        <v>5.16938869594152</v>
+        <v>5.38230449253923</v>
       </c>
       <c r="J66" s="20" t="n">
         <f aca="false">J64*J65</f>
-        <v>4.93588597831843</v>
+        <v>5.13601432162153</v>
       </c>
       <c r="K66" s="20" t="n">
         <f aca="false">K64*K65</f>
-        <v>4.67005882615337</v>
+        <v>4.85940905428091</v>
       </c>
       <c r="L66" s="20"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
-        <v>176.958792990269</v>
+        <v>184.133689296549</v>
       </c>
       <c r="C67" s="1" t="str">
         <f aca="false">IF($B$10&gt;L57,"","Discount rate must exceed terminal growth")</f>
@@ -3031,47 +3022,47 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
-        <v>91.2540230397786</v>
+        <v>94.9539700261787</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
-        <v>98.5103576861102</v>
+        <v>109.21155096859</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
-        <v>476.978442289789</v>
+        <v>532.479526906825</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
-        <v>0.602723214629423</v>
+        <v>0.788224223080986</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
@@ -3085,68 +3076,68 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
-        <v>149.896015253973</v>
+        <v>181.632914629396</v>
       </c>
       <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
-        <v>-0.496325615315694</v>
+        <v>-0.390022787287517</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
-        <v>330.62375234843</v>
+        <v>379.866227557491</v>
       </c>
       <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
-        <v>0.110948244647871</v>
+        <v>0.275703487784165</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
-        <v>476.978442289789</v>
+        <v>532.479526906825</v>
       </c>
       <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
-        <v>0.602723214629423</v>
+        <v>0.788224223080986</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
-        <v>330.62375234843</v>
+        <v>379.866227557491</v>
       </c>
       <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
-        <v>0.110948244647871</v>
+        <v>0.275703487784165</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
-        <v>0.607852329339917</v>
+        <v>0.606907986023661</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3186,104 +3177,104 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B83" s="8" t="n">
         <f aca="false">IF(B82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+B82)^$B$16:$K$16)+$L46/(B82-$L39)/(1+B82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>678.564795340189</v>
+        <v>745.65839541152</v>
       </c>
       <c r="C83" s="8" t="n">
         <f aca="false">IF(C82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+C82)^$B$16:$K$16)+$L46/(C82-$L39)/(1+C82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>479.257586455029</v>
+        <v>536.132015349444</v>
       </c>
       <c r="D83" s="8" t="n">
         <f aca="false">IF(D82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+D82)^$B$16:$K$16)+$L46/(D82-$L39)/(1+D82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>352.541019348523</v>
+        <v>402.909773281145</v>
       </c>
       <c r="E83" s="8" t="n">
         <f aca="false">IF(E82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+E82)^$B$16:$K$16)+$L46/(E82-$L39)/(1+E82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>264.907928570543</v>
+        <v>310.770882452973</v>
       </c>
       <c r="F83" s="8" t="n">
         <f aca="false">IF(F82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+F82)^$B$16:$K$16)+$L46/(F82-$L39)/(1+F82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>200.721745461392</v>
+        <v>243.279056244114</v>
       </c>
       <c r="G83" s="8" t="n">
         <f aca="false">IF(G82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+G82)^$B$16:$K$16)+$L46/(G82-$L39)/(1+G82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>151.70438330211</v>
+        <v>191.732805762011</v>
       </c>
       <c r="H83" s="8" t="n">
         <f aca="false">IF(H82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+H82)^$B$16:$K$16)+$L46/(H82-$L39)/(1+H82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>113.063352117941</v>
+        <v>151.094495807724</v>
       </c>
       <c r="I83" s="8" t="n">
         <f aca="false">IF(I82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+I82)^$B$16:$K$16)+$L46/(I82-$L39)/(1+I82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>81.8319501680315</v>
+        <v>118.245653794937</v>
       </c>
       <c r="J83" s="8" t="n">
         <f aca="false">IF(J82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+J82)^$B$16:$K$16)+$L46/(J82-$L39)/(1+J82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>56.0754420679196</v>
+        <v>91.152551690006</v>
       </c>
       <c r="K83" s="8" t="n">
         <f aca="false">IF(K82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+K82)^$B$16:$K$16)+$L46/(K82-$L39)/(1+K82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>34.4782711100344</v>
+        <v>68.4323081791424</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="7" t="n">
         <f aca="false">IFERROR(B83/$B$4-1,"n/a")</f>
-        <v>1.28008533237072</v>
+        <v>1.50414210770568</v>
       </c>
       <c r="C84" s="7" t="n">
         <f aca="false">IFERROR(C83/$B$4-1,"n/a")</f>
-        <v>0.610381500495722</v>
+        <v>0.800490362862088</v>
       </c>
       <c r="D84" s="7" t="n">
         <f aca="false">IFERROR(D83/$B$4-1,"n/a")</f>
-        <v>0.184593737835461</v>
+        <v>0.353090550697332</v>
       </c>
       <c r="E84" s="7" t="n">
         <f aca="false">IFERROR(E83/$B$4-1,"n/a")</f>
-        <v>-0.109867345741694</v>
+        <v>0.0436608202739472</v>
       </c>
       <c r="F84" s="7" t="n">
         <f aca="false">IFERROR(F83/$B$4-1,"n/a")</f>
-        <v>-0.325543100884084</v>
+        <v>-0.182996755065607</v>
       </c>
       <c r="G84" s="7" t="n">
         <f aca="false">IFERROR(G83/$B$4-1,"n/a")</f>
-        <v>-0.490249211867711</v>
+        <v>-0.35610435651002</v>
       </c>
       <c r="H84" s="7" t="n">
         <f aca="false">IFERROR(H83/$B$4-1,"n/a")</f>
-        <v>-0.620089205094199</v>
+        <v>-0.492579857582281</v>
       </c>
       <c r="I84" s="7" t="n">
         <f aca="false">IFERROR(I83/$B$4-1,"n/a")</f>
-        <v>-0.725031668930188</v>
+        <v>-0.602896014390512</v>
       </c>
       <c r="J84" s="7" t="n">
         <f aca="false">IFERROR(J83/$B$4-1,"n/a")</f>
-        <v>-0.811577621115507</v>
+        <v>-0.693882689021708</v>
       </c>
       <c r="K84" s="7" t="n">
         <f aca="false">IFERROR(K83/$B$4-1,"n/a")</f>
-        <v>-0.884147540834212</v>
+        <v>-0.770184007189635</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" s="26" t="n">
         <f aca="false">IFERROR(IF(MATCH($B$4,$B$83:$K$83,-1)=10,"above 14%",INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1))+(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-$B$4)/(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1)+1))*(INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)+1)-INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)))),"below 5%")</f>
-        <v>0.0762688670296594</v>
+        <v>0.0819262899203144</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3312,165 +3303,165 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>0.0503</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0.012</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>0.06</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B14" s="27" t="n">
         <v>0.8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">0.67*IF(ISNUMBER(B14),B14,B13)+0.33</f>
         <v>0.866</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">IF($B$6=1,IF(ISNUMBER(B14),B14,B13),B15)</f>
         <v>0.866</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
         <v>0.0936</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
         <v>0.0623</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">LNG!B9</f>
         <v>0.18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
@@ -3480,85 +3471,85 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">LNG!B4*LNG!B6</f>
-        <v>61.46436065</v>
+        <v>61.072627</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" s="30" t="n">
-        <v>27.97</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">B21/(B21+B22)</f>
-        <v>0.687256667384696</v>
+        <v>0.718479288881272</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22/(B21+B22)</f>
-        <v>0.312743332615304</v>
+        <v>0.281520711118728</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
-        <v>0.080304029957193</v>
+        <v>0.0816314284874984</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" s="31" t="n">
         <v>0.0722</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
         <v>0.0722</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="1" t="str">
         <f aca="false">IF(B27&gt;MAX(LNG!L21,LNG!L39,LNG!L57),"OK","WACC must exceed growth")</f>
@@ -3568,14 +3559,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
         <v>0.0722</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
